--- a/new_file.xlsx
+++ b/new_file.xlsx
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Service Quality</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Product Quality</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Product Quality</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Others</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Product Quality</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Product Quality</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Product</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Category:</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Category:</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Service Quality</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Service Quality</t>
+          <t>Service</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Category:</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Product</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Agent</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Agent</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Service Quality</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Product Quality</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Product Quality</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Service Quality</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Agent</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Product Quality</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Category:</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Service Quality</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Product Quality</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Category:</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Category:</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Category:</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Category:</t>
+          <t>Product Quality</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Product Quality</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Category:</t>
+          <t>Product</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Product Quality</t>
+          <t>Product</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Product Quality</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Service Quality</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Product Quality</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Category:</t>
+          <t>Service</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Category:</t>
+          <t>Service Quality</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2125,7 @@
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Category:</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Category:</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2190,7 @@
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -2203,7 +2203,7 @@
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Service Quality</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Category:</t>
+          <t>Agent</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -2255,7 +2255,7 @@
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2268,7 @@
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2320,7 @@
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Agent</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2385,7 @@
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -2437,7 +2437,7 @@
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Category:</t>
+          <t>Agent</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Category:</t>
+          <t>Others</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Category:</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2502,7 @@
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -2567,7 +2567,7 @@
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Category:</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Category:</t>
+          <t>Service Quality</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Product Quality</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2710,7 @@
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Service Quality</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Service Quality</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Category:</t>
+          <t>Service Quality</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -2840,7 +2840,7 @@
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Category:</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2970,7 @@
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
       <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -3022,7 +3022,7 @@
       <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Category:</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -3074,7 +3074,7 @@
       <c r="B174" t="inlineStr"/>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Category:</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3113,7 @@
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3139,7 @@
       <c r="B179" t="inlineStr"/>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -3178,7 +3178,7 @@
       <c r="B182" t="inlineStr"/>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3204,7 @@
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3230,7 @@
       <c r="B186" t="inlineStr"/>
       <c r="C186" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Agent</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       <c r="B187" t="inlineStr"/>
       <c r="C187" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
       <c r="B190" t="inlineStr"/>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3308,7 @@
       <c r="B192" t="inlineStr"/>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Service Quality</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3334,7 @@
       <c r="B194" t="inlineStr"/>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3347,7 @@
       <c r="B195" t="inlineStr"/>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       <c r="B196" t="inlineStr"/>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Category:</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       <c r="B197" t="inlineStr"/>
       <c r="C197" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3399,7 @@
       <c r="B199" t="inlineStr"/>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       <c r="B200" t="inlineStr"/>
       <c r="C200" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -3425,7 +3425,7 @@
       <c r="B201" t="inlineStr"/>
       <c r="C201" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -3438,7 +3438,7 @@
       <c r="B202" t="inlineStr"/>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Category:</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       <c r="B203" t="inlineStr"/>
       <c r="C203" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       <c r="B204" t="inlineStr"/>
       <c r="C204" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -3490,7 +3490,7 @@
       <c r="B206" t="inlineStr"/>
       <c r="C206" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3503,7 @@
       <c r="B207" t="inlineStr"/>
       <c r="C207" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -3542,7 +3542,7 @@
       <c r="B210" t="inlineStr"/>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3555,7 @@
       <c r="B211" t="inlineStr"/>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3568,7 @@
       <c r="B212" t="inlineStr"/>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       <c r="B213" t="inlineStr"/>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -3594,7 +3594,7 @@
       <c r="B214" t="inlineStr"/>
       <c r="C214" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Others</t>
         </is>
       </c>
     </row>
@@ -3607,7 +3607,7 @@
       <c r="B215" t="inlineStr"/>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3633,7 @@
       <c r="B217" t="inlineStr"/>
       <c r="C217" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Others</t>
         </is>
       </c>
     </row>
@@ -3659,7 +3659,7 @@
       <c r="B219" t="inlineStr"/>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>No Topic Identified (Gemini)</t>
         </is>
       </c>
     </row>
@@ -3672,7 +3672,7 @@
       <c r="B220" t="inlineStr"/>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       <c r="B222" t="inlineStr"/>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       <c r="B223" t="inlineStr"/>
       <c r="C223" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Agent</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       <c r="B224" t="inlineStr"/>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       <c r="B225" t="inlineStr"/>
       <c r="C225" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3750,7 @@
       <c r="B226" t="inlineStr"/>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Category:</t>
+          <t>Service</t>
         </is>
       </c>
     </row>
@@ -3776,7 +3776,7 @@
       <c r="B228" t="inlineStr"/>
       <c r="C228" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
@@ -3789,7 +3789,7 @@
       <c r="B229" t="inlineStr"/>
       <c r="C229" t="inlineStr">
         <is>
-          <t>No Topic Identified (Gemini)</t>
+          <t>Category:</t>
         </is>
       </c>
     </row>
